--- a/output/pdf_financials_xlsx/AUCU.xlsx
+++ b/output/pdf_financials_xlsx/AUCU.xlsx
@@ -1933,10 +1933,10 @@
         <v>0</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>1.972051</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>1.949644</v>
       </c>
     </row>
     <row r="93">
@@ -3114,7 +3114,11 @@
           <t>Reserves (Note 8)</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/AUCU.xlsx
+++ b/output/pdf_financials_xlsx/AUCU.xlsx
@@ -577,13 +577,13 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.635571</v>
+        <v>1.299568</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.43894</v>
+        <v>1.434445</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.440394</v>
+        <v>0.843475</v>
       </c>
     </row>
     <row r="11">
@@ -593,13 +593,13 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>-0.635571</v>
+        <v>-1.299568</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-0.43894</v>
+        <v>-1.434445</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-0.440394</v>
+        <v>-0.843475</v>
       </c>
     </row>
     <row r="12">
@@ -5027,17 +5027,17 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E78" s="5" t="n">
-        <v>-1.299568</v>
+        <v>1.299568</v>
       </c>
       <c r="F78" s="5" t="n">
-        <v>-1.434445</v>
+        <v>1.434445</v>
       </c>
       <c r="G78" s="5" t="n">
-        <v>-0.843475</v>
+        <v>0.843475</v>
       </c>
     </row>
     <row r="79">

--- a/output/pdf_financials_xlsx/AUCU.xlsx
+++ b/output/pdf_financials_xlsx/AUCU.xlsx
@@ -1512,10 +1512,10 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.221199</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.159356</v>
       </c>
       <c r="D67" s="3" t="n">
         <v>0</v>
@@ -4599,7 +4599,11 @@
           <t>Proceeds from private placement</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr"/>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E64" s="5" t="n">
         <v>1.77675</v>
       </c>
